--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="1" r:id="R3960692ad2f94b89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="1" r:id="Rfa0aa16de4ad4813"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -124,7 +124,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="17">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -176,8 +176,38 @@
         <x:fgColor rgb="FFF5F8FB"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="11">
+  <x:borders count="12">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -271,11 +301,25 @@
         <x:color rgb="FFD7E0E8"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="120">
+  <x:cellXfs count="134">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -798,6 +842,53 @@
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1019,891 +1110,1300 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="23" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="27" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="23" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="10" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="8" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="8" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="8" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="36" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="36" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="85" t="str">
+      <x:c r="A1" s="129" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B1" s="85" t="str">
+      <x:c r="B1" s="129" t="str">
         <x:v>full_name</x:v>
       </x:c>
-      <x:c r="C1" s="85" t="str">
+      <x:c r="C1" s="129" t="str">
         <x:v>value_type</x:v>
       </x:c>
-      <x:c r="D1" s="85" t="str">
+      <x:c r="D1" s="129" t="str">
         <x:v>read_schema_from_file</x:v>
       </x:c>
-      <x:c r="E1" s="85" t="str">
+      <x:c r="E1" s="129" t="str">
         <x:v>input</x:v>
       </x:c>
-      <x:c r="F1" s="85" t="str">
+      <x:c r="F1" s="129" t="str">
         <x:v>index</x:v>
       </x:c>
-      <x:c r="G1" s="85" t="str">
+      <x:c r="G1" s="129" t="str">
         <x:v>mode</x:v>
       </x:c>
-      <x:c r="H1" s="85" t="str">
+      <x:c r="H1" s="129" t="str">
         <x:v>group</x:v>
       </x:c>
-      <x:c r="I1" s="85" t="str">
+      <x:c r="I1" s="129" t="str">
         <x:v>comment</x:v>
       </x:c>
-      <x:c r="J1" s="85" t="str">
+      <x:c r="J1" s="129" t="str">
         <x:v>tags</x:v>
       </x:c>
-      <x:c r="K1" s="85" t="str">
+      <x:c r="K1" s="129" t="str">
         <x:v>output</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="87" t="str">
+      <x:c r="A2" s="131" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B2" s="87" t="str">
+      <x:c r="B2" s="131" t="str">
         <x:v>完整表名</x:v>
       </x:c>
-      <x:c r="C2" s="87" t="str">
+      <x:c r="C2" s="131" t="str">
         <x:v>记录类型</x:v>
       </x:c>
-      <x:c r="D2" s="87" t="str">
+      <x:c r="D2" s="131" t="str">
         <x:v>从业务表读取定义</x:v>
       </x:c>
-      <x:c r="E2" s="87" t="str">
+      <x:c r="E2" s="131" t="str">
         <x:v>输入文件</x:v>
       </x:c>
-      <x:c r="F2" s="87" t="str">
+      <x:c r="F2" s="131" t="str">
         <x:v>索引字段</x:v>
       </x:c>
-      <x:c r="G2" s="87" t="str">
+      <x:c r="G2" s="131" t="str">
         <x:v>模式</x:v>
       </x:c>
-      <x:c r="H2" s="87" t="str">
+      <x:c r="H2" s="131" t="str">
         <x:v>分组</x:v>
       </x:c>
-      <x:c r="I2" s="87" t="str">
+      <x:c r="I2" s="131" t="str">
         <x:v>说明</x:v>
       </x:c>
-      <x:c r="J2" s="87"/>
-      <x:c r="K2" s="87" t="str">
+      <x:c r="J2" s="131"/>
+      <x:c r="K2" s="131" t="str">
         <x:v>输出文件</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="90" t="str">
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="133" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B3" s="91"/>
-      <x:c r="C3" s="91"/>
-      <x:c r="D3" s="91" t="str">
+      <x:c r="B3" s="133"/>
+      <x:c r="C3" s="133"/>
+      <x:c r="D3" s="133" t="str">
         <x:v>必须为 true</x:v>
       </x:c>
-      <x:c r="E3" s="91"/>
-      <x:c r="F3" s="91" t="str">
+      <x:c r="E3" s="133"/>
+      <x:c r="F3" s="133" t="str">
         <x:v>统一使用 id</x:v>
       </x:c>
-      <x:c r="G3" s="91" t="str">
+      <x:c r="G3" s="133" t="str">
         <x:v>统一使用 map</x:v>
       </x:c>
-      <x:c r="H3" s="91" t="str">
+      <x:c r="H3" s="133" t="str">
         <x:v>客户端 c</x:v>
       </x:c>
-      <x:c r="I3" s="91"/>
-      <x:c r="J3" s="91"/>
-      <x:c r="K3" s="91"/>
-    </x:row>
-    <x:row r="4" ht="54" customHeight="1">
-      <x:c r="A4" s="95"/>
-      <x:c r="B4" s="96" t="str">
+      <x:c r="I3" s="133"/>
+      <x:c r="J3" s="133"/>
+      <x:c r="K3" s="133"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="120"/>
+      <x:c r="B4" s="120" t="str">
         <x:v>TbResource</x:v>
       </x:c>
-      <x:c r="C4" s="96" t="str">
+      <x:c r="C4" s="120" t="str">
         <x:v>ResourceConfig</x:v>
       </x:c>
-      <x:c r="D4" s="97" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4" s="96" t="str">
+      <x:c r="D4" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="120" t="str">
         <x:v>Tables/z_资源_ResourceConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F4" s="96" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G4" s="96" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H4" s="96" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I4" s="96" t="str">
+      <x:c r="F4" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G4" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H4" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I4" s="120" t="str">
         <x:v>TbResource generated from Excel</x:v>
       </x:c>
-      <x:c r="J4" s="96"/>
-      <x:c r="K4" s="96"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="118"/>
-      <x:c r="B5" s="118" t="str">
+      <x:c r="J4" s="120"/>
+      <x:c r="K4" s="120"/>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="120"/>
+      <x:c r="B5" s="120" t="str">
         <x:v>TbAttribute</x:v>
       </x:c>
-      <x:c r="C5" s="118" t="str">
+      <x:c r="C5" s="120" t="str">
         <x:v>AttributeConfig</x:v>
       </x:c>
-      <x:c r="D5" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E5" s="118" t="str">
+      <x:c r="D5" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="120" t="str">
         <x:v>Tables/s_属性_AttributeConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F5" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G5" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H5" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I5" s="118" t="str">
+      <x:c r="F5" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G5" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H5" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I5" s="120" t="str">
         <x:v>TbAttribute generated from Excel</x:v>
       </x:c>
-      <x:c r="J5" s="118"/>
-      <x:c r="K5" s="118"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="118"/>
-      <x:c r="B6" s="118" t="str">
+      <x:c r="J5" s="120"/>
+      <x:c r="K5" s="120"/>
+    </x:row>
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="120"/>
+      <x:c r="B6" s="120" t="str">
         <x:v>TbItem</x:v>
       </x:c>
-      <x:c r="C6" s="118" t="str">
+      <x:c r="C6" s="120" t="str">
         <x:v>ItemConfig</x:v>
       </x:c>
-      <x:c r="D6" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E6" s="118" t="str">
+      <x:c r="D6" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" s="120" t="str">
         <x:v>Tables/w_物品_ItemConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F6" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G6" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H6" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I6" s="118" t="str">
+      <x:c r="F6" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G6" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H6" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I6" s="120" t="str">
         <x:v>TbItem generated from Excel</x:v>
       </x:c>
-      <x:c r="J6" s="118"/>
-      <x:c r="K6" s="118"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="118"/>
-      <x:c r="B7" s="118" t="str">
+      <x:c r="J6" s="120"/>
+      <x:c r="K6" s="120"/>
+    </x:row>
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="120"/>
+      <x:c r="B7" s="120" t="str">
         <x:v>TbAnimationClip</x:v>
       </x:c>
-      <x:c r="C7" s="118" t="str">
+      <x:c r="C7" s="120" t="str">
         <x:v>AnimationClipConfig</x:v>
       </x:c>
-      <x:c r="D7" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E7" s="118" t="str">
+      <x:c r="D7" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" s="120" t="str">
         <x:v>Tables/d_动画片段_AnimationClipConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F7" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G7" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H7" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I7" s="118" t="str">
+      <x:c r="F7" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G7" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H7" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I7" s="120" t="str">
         <x:v>TbAnimationClip generated from Excel</x:v>
       </x:c>
-      <x:c r="J7" s="118"/>
-      <x:c r="K7" s="118"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="118"/>
-      <x:c r="B8" s="118" t="str">
+      <x:c r="J7" s="120"/>
+      <x:c r="K7" s="120"/>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="120"/>
+      <x:c r="B8" s="120" t="str">
         <x:v>TbVisualSet</x:v>
       </x:c>
-      <x:c r="C8" s="118" t="str">
+      <x:c r="C8" s="120" t="str">
         <x:v>VisualSetConfig</x:v>
       </x:c>
-      <x:c r="D8" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E8" s="118" t="str">
+      <x:c r="D8" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="120" t="str">
         <x:v>Tables/b_表现集合_VisualSetConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F8" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G8" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H8" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I8" s="118" t="str">
+      <x:c r="F8" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G8" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H8" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I8" s="120" t="str">
         <x:v>TbVisualSet generated from Excel</x:v>
       </x:c>
-      <x:c r="J8" s="118"/>
-      <x:c r="K8" s="118"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="118"/>
-      <x:c r="B9" s="118" t="str">
+      <x:c r="J8" s="120"/>
+      <x:c r="K8" s="120"/>
+    </x:row>
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="120"/>
+      <x:c r="B9" s="120" t="str">
         <x:v>TbMap</x:v>
       </x:c>
-      <x:c r="C9" s="118" t="str">
+      <x:c r="C9" s="120" t="str">
         <x:v>MapConfig</x:v>
       </x:c>
-      <x:c r="D9" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E9" s="118" t="str">
+      <x:c r="D9" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" s="120" t="str">
         <x:v>Tables/d_地图_MapConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F9" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G9" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H9" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I9" s="118" t="str">
+      <x:c r="F9" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G9" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H9" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I9" s="120" t="str">
         <x:v>TbMap generated from Excel</x:v>
       </x:c>
-      <x:c r="J9" s="118"/>
-      <x:c r="K9" s="118"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="118"/>
-      <x:c r="B10" s="118" t="str">
+      <x:c r="J9" s="120"/>
+      <x:c r="K9" s="120"/>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="120"/>
+      <x:c r="B10" s="120" t="str">
         <x:v>TbCharacter</x:v>
       </x:c>
-      <x:c r="C10" s="118" t="str">
+      <x:c r="C10" s="120" t="str">
         <x:v>CharacterConfig</x:v>
       </x:c>
-      <x:c r="D10" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E10" s="118" t="str">
+      <x:c r="D10" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E10" s="120" t="str">
         <x:v>Tables/j_角色_CharacterConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F10" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G10" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H10" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I10" s="118" t="str">
+      <x:c r="F10" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G10" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H10" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I10" s="120" t="str">
         <x:v>TbCharacter generated from Excel</x:v>
       </x:c>
-      <x:c r="J10" s="118"/>
-      <x:c r="K10" s="118"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="118"/>
-      <x:c r="B11" s="118" t="str">
+      <x:c r="J10" s="120"/>
+      <x:c r="K10" s="120"/>
+    </x:row>
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="120"/>
+      <x:c r="B11" s="120" t="str">
         <x:v>TbMonster</x:v>
       </x:c>
-      <x:c r="C11" s="118" t="str">
+      <x:c r="C11" s="120" t="str">
         <x:v>MonsterConfig</x:v>
       </x:c>
-      <x:c r="D11" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E11" s="118" t="str">
+      <x:c r="D11" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E11" s="120" t="str">
         <x:v>Tables/g_怪物_MonsterConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F11" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G11" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H11" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I11" s="118" t="str">
+      <x:c r="F11" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G11" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H11" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I11" s="120" t="str">
         <x:v>TbMonster generated from Excel</x:v>
       </x:c>
-      <x:c r="J11" s="118"/>
-      <x:c r="K11" s="118"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="118"/>
-      <x:c r="B12" s="118" t="str">
+      <x:c r="J11" s="120"/>
+      <x:c r="K11" s="120"/>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="120"/>
+      <x:c r="B12" s="120" t="str">
         <x:v>TbSkill</x:v>
       </x:c>
-      <x:c r="C12" s="118" t="str">
+      <x:c r="C12" s="120" t="str">
         <x:v>SkillConfig</x:v>
       </x:c>
-      <x:c r="D12" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E12" s="118" t="str">
+      <x:c r="D12" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" s="120" t="str">
         <x:v>Tables/j_技能_SkillConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F12" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G12" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H12" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I12" s="118" t="str">
+      <x:c r="F12" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G12" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H12" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I12" s="120" t="str">
         <x:v>TbSkill generated from Excel</x:v>
       </x:c>
-      <x:c r="J12" s="118"/>
-      <x:c r="K12" s="118"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="118"/>
-      <x:c r="B13" s="118" t="str">
+      <x:c r="J12" s="120"/>
+      <x:c r="K12" s="120"/>
+    </x:row>
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13" s="120"/>
+      <x:c r="B13" s="120" t="str">
         <x:v>TbStage</x:v>
       </x:c>
-      <x:c r="C13" s="118" t="str">
+      <x:c r="C13" s="120" t="str">
         <x:v>StageConfig</x:v>
       </x:c>
-      <x:c r="D13" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E13" s="118" t="str">
+      <x:c r="D13" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E13" s="120" t="str">
         <x:v>Tables/g_关卡_StageConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F13" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G13" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H13" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I13" s="118" t="str">
+      <x:c r="F13" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G13" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H13" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I13" s="120" t="str">
         <x:v>TbStage generated from Excel</x:v>
       </x:c>
-      <x:c r="J13" s="118"/>
-      <x:c r="K13" s="118"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="118"/>
-      <x:c r="B14" s="118" t="str">
+      <x:c r="J13" s="120"/>
+      <x:c r="K13" s="120"/>
+    </x:row>
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="120"/>
+      <x:c r="B14" s="120" t="str">
         <x:v>GameConfig</x:v>
       </x:c>
-      <x:c r="C14" s="118" t="str">
+      <x:c r="C14" s="120" t="str">
         <x:v>GameConfigData</x:v>
       </x:c>
-      <x:c r="D14" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E14" s="118" t="str">
+      <x:c r="D14" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E14" s="120" t="str">
         <x:v>Tables/y_游戏配置_GameConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F14" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G14" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H14" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I14" s="118" t="str">
+      <x:c r="F14" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G14" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H14" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I14" s="120" t="str">
         <x:v>GameConfig generated from Excel</x:v>
       </x:c>
-      <x:c r="J14" s="118"/>
-      <x:c r="K14" s="118"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="118"/>
-      <x:c r="B15" s="118" t="str">
+      <x:c r="J14" s="120"/>
+      <x:c r="K14" s="120"/>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="120"/>
+      <x:c r="B15" s="120" t="str">
         <x:v>TbPerformanceScenario</x:v>
       </x:c>
-      <x:c r="C15" s="118" t="str">
+      <x:c r="C15" s="120" t="str">
         <x:v>PerformanceScenarioConfig</x:v>
       </x:c>
-      <x:c r="D15" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E15" s="118" t="str">
+      <x:c r="D15" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E15" s="120" t="str">
         <x:v>Tables/x_性能测试_PerformanceScenarioConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F15" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G15" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H15" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I15" s="118" t="str">
+      <x:c r="F15" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G15" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H15" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I15" s="120" t="str">
         <x:v>TbPerformanceScenario generated from Excel</x:v>
       </x:c>
-      <x:c r="J15" s="118"/>
-      <x:c r="K15" s="118"/>
-    </x:row>
-    <x:row r="16" ht="45" customHeight="1">
-      <x:c r="A16" s="118"/>
-      <x:c r="B16" s="118" t="str">
+      <x:c r="J15" s="120"/>
+      <x:c r="K15" s="120"/>
+    </x:row>
+    <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16" s="120"/>
+      <x:c r="B16" s="120" t="str">
         <x:v>TbAttributeProfile</x:v>
       </x:c>
-      <x:c r="C16" s="118" t="str">
+      <x:c r="C16" s="120" t="str">
         <x:v>AttributeProfileConfig</x:v>
       </x:c>
-      <x:c r="D16" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E16" s="118" t="str">
+      <x:c r="D16" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E16" s="120" t="str">
         <x:v>Tables/s_属性方案_AttributeProfileConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F16" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G16" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H16" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I16" s="118" t="str">
+      <x:c r="F16" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G16" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H16" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I16" s="120" t="str">
         <x:v>TbAttributeProfile generated from Excel</x:v>
       </x:c>
-      <x:c r="J16" s="118"/>
-      <x:c r="K16" s="118"/>
-    </x:row>
-    <x:row r="17" ht="45" customHeight="1">
-      <x:c r="A17" s="118"/>
-      <x:c r="B17" s="118" t="str">
+      <x:c r="J16" s="120"/>
+      <x:c r="K16" s="120"/>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="120"/>
+      <x:c r="B17" s="120" t="str">
         <x:v>TbSkillCombat</x:v>
       </x:c>
-      <x:c r="C17" s="118" t="str">
+      <x:c r="C17" s="120" t="str">
         <x:v>SkillCombatConfig</x:v>
       </x:c>
-      <x:c r="D17" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E17" s="118" t="str">
+      <x:c r="D17" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E17" s="120" t="str">
         <x:v>Tables/j_技能战斗_SkillCombatConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F17" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G17" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H17" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I17" s="118" t="str">
+      <x:c r="F17" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G17" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H17" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I17" s="120" t="str">
         <x:v>TbSkillCombat generated from Excel</x:v>
       </x:c>
-      <x:c r="J17" s="118"/>
-      <x:c r="K17" s="118"/>
-    </x:row>
-    <x:row r="18" ht="45" customHeight="1">
-      <x:c r="A18" s="118"/>
-      <x:c r="B18" s="118" t="str">
+      <x:c r="J17" s="120"/>
+      <x:c r="K17" s="120"/>
+    </x:row>
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="120"/>
+      <x:c r="B18" s="120" t="str">
         <x:v>TbCombatRules</x:v>
       </x:c>
-      <x:c r="C18" s="118" t="str">
+      <x:c r="C18" s="120" t="str">
         <x:v>CombatRulesConfig</x:v>
       </x:c>
-      <x:c r="D18" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E18" s="118" t="str">
+      <x:c r="D18" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E18" s="120" t="str">
         <x:v>Tables/z_战斗规则_CombatRulesConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F18" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G18" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H18" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I18" s="118" t="str">
+      <x:c r="F18" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G18" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H18" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I18" s="120" t="str">
         <x:v>TbCombatRules generated from Excel</x:v>
       </x:c>
-      <x:c r="J18" s="118"/>
-      <x:c r="K18" s="118"/>
-    </x:row>
-    <x:row r="19" ht="72" customHeight="1">
-      <x:c r="A19" s="118"/>
-      <x:c r="B19" s="118" t="str">
+      <x:c r="J18" s="120"/>
+      <x:c r="K18" s="120"/>
+    </x:row>
+    <x:row r="19" ht="24" customHeight="1">
+      <x:c r="A19" s="120"/>
+      <x:c r="B19" s="120" t="str">
         <x:v>TbAnimationDirection</x:v>
       </x:c>
-      <x:c r="C19" s="118" t="str">
+      <x:c r="C19" s="120" t="str">
         <x:v>AnimationDirectionConfig</x:v>
       </x:c>
-      <x:c r="D19" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E19" s="118" t="str">
+      <x:c r="D19" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E19" s="120" t="str">
         <x:v>Tables/d_动画方向_AnimationDirectionConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F19" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G19" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H19" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I19" s="118" t="str">
+      <x:c r="F19" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G19" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H19" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I19" s="120" t="str">
         <x:v>TbAnimationDirection generated from Excel</x:v>
       </x:c>
-      <x:c r="J19" s="118"/>
-      <x:c r="K19" s="118"/>
-    </x:row>
-    <x:row r="20" ht="72" customHeight="1">
-      <x:c r="A20" s="118"/>
-      <x:c r="B20" s="118" t="str">
+      <x:c r="J19" s="120"/>
+      <x:c r="K19" s="120"/>
+    </x:row>
+    <x:row r="20" ht="24" customHeight="1">
+      <x:c r="A20" s="120"/>
+      <x:c r="B20" s="120" t="str">
         <x:v>TbCombatPresentation</x:v>
       </x:c>
-      <x:c r="C20" s="118" t="str">
+      <x:c r="C20" s="120" t="str">
         <x:v>CombatPresentationConfig</x:v>
       </x:c>
-      <x:c r="D20" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E20" s="118" t="str">
+      <x:c r="D20" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E20" s="120" t="str">
         <x:v>Tables/z_战斗表现_CombatPresentationConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F20" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G20" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H20" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I20" s="118" t="str">
+      <x:c r="F20" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G20" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H20" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I20" s="120" t="str">
         <x:v>TbCombatPresentation generated from Excel</x:v>
       </x:c>
-      <x:c r="J20" s="118"/>
-      <x:c r="K20" s="118"/>
-    </x:row>
-    <x:row r="21" ht="72" customHeight="1">
-      <x:c r="A21" s="118"/>
-      <x:c r="B21" s="118" t="str">
+      <x:c r="J20" s="120"/>
+      <x:c r="K20" s="120"/>
+    </x:row>
+    <x:row r="21" ht="24" customHeight="1">
+      <x:c r="A21" s="120"/>
+      <x:c r="B21" s="120" t="str">
         <x:v>TbAttackDirection</x:v>
       </x:c>
-      <x:c r="C21" s="118" t="str">
+      <x:c r="C21" s="120" t="str">
         <x:v>AttackDirectionConfig</x:v>
       </x:c>
-      <x:c r="D21" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E21" s="118" t="str">
+      <x:c r="D21" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E21" s="120" t="str">
         <x:v>Tables/d_攻击方向_AttackDirectionConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F21" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G21" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H21" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I21" s="118" t="str">
+      <x:c r="F21" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G21" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H21" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I21" s="120" t="str">
         <x:v>TbAttackDirection generated from Excel</x:v>
       </x:c>
-      <x:c r="J21" s="118"/>
-      <x:c r="K21" s="118"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="118"/>
-      <x:c r="B22" s="118" t="str">
+      <x:c r="J21" s="120"/>
+      <x:c r="K21" s="120"/>
+    </x:row>
+    <x:row r="22" ht="24" customHeight="1">
+      <x:c r="A22" s="120"/>
+      <x:c r="B22" s="120" t="str">
         <x:v>TbHeroWeapon</x:v>
       </x:c>
-      <x:c r="C22" s="118" t="str">
+      <x:c r="C22" s="120" t="str">
         <x:v>HeroWeaponConfig</x:v>
       </x:c>
-      <x:c r="D22" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E22" s="118" t="str">
+      <x:c r="D22" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E22" s="120" t="str">
         <x:v>Tables/h_神将武器_HeroWeaponConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F22" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G22" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H22" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I22" s="118" t="str">
+      <x:c r="F22" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G22" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H22" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I22" s="120" t="str">
         <x:v>神将五档武器与本体映射</x:v>
       </x:c>
-      <x:c r="J22" s="118"/>
-      <x:c r="K22" s="118"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="118"/>
-      <x:c r="B23" s="118" t="str">
+      <x:c r="J22" s="120"/>
+      <x:c r="K22" s="120"/>
+    </x:row>
+    <x:row r="23" ht="24" customHeight="1">
+      <x:c r="A23" s="120"/>
+      <x:c r="B23" s="120" t="str">
         <x:v>TbStageRule</x:v>
       </x:c>
-      <x:c r="C23" s="118" t="str">
+      <x:c r="C23" s="120" t="str">
         <x:v>StageRuleConfig</x:v>
       </x:c>
-      <x:c r="D23" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E23" s="118" t="str">
+      <x:c r="D23" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E23" s="120" t="str">
         <x:v>Tables/g_关卡规则_StageRuleConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F23" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G23" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H23" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I23" s="118" t="str">
+      <x:c r="F23" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G23" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H23" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I23" s="120" t="str">
         <x:v>TbStageRule generated from Excel</x:v>
       </x:c>
-      <x:c r="J23" s="118"/>
-      <x:c r="K23" s="118"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="118"/>
-      <x:c r="B24" s="118" t="str">
+      <x:c r="J23" s="120"/>
+      <x:c r="K23" s="120"/>
+    </x:row>
+    <x:row r="24" ht="24" customHeight="1">
+      <x:c r="A24" s="120"/>
+      <x:c r="B24" s="120" t="str">
         <x:v>TbSpawnPhase</x:v>
       </x:c>
-      <x:c r="C24" s="118" t="str">
+      <x:c r="C24" s="120" t="str">
         <x:v>SpawnPhaseConfig</x:v>
       </x:c>
-      <x:c r="D24" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E24" s="118" t="str">
+      <x:c r="D24" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E24" s="120" t="str">
         <x:v>Tables/s_刷新阶段_SpawnPhaseConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F24" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G24" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H24" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I24" s="118" t="str">
+      <x:c r="F24" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G24" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H24" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I24" s="120" t="str">
         <x:v>TbSpawnPhase generated from Excel</x:v>
       </x:c>
-      <x:c r="J24" s="118"/>
-      <x:c r="K24" s="118"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="118"/>
-      <x:c r="B25" s="118" t="str">
+      <x:c r="J24" s="120"/>
+      <x:c r="K24" s="120"/>
+    </x:row>
+    <x:row r="25" ht="24" customHeight="1">
+      <x:c r="A25" s="120"/>
+      <x:c r="B25" s="120" t="str">
         <x:v>TbBossEncounter</x:v>
       </x:c>
-      <x:c r="C25" s="118" t="str">
+      <x:c r="C25" s="120" t="str">
         <x:v>BossEncounterConfig</x:v>
       </x:c>
-      <x:c r="D25" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E25" s="118" t="str">
+      <x:c r="D25" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E25" s="120" t="str">
         <x:v>Tables/b_Boss遭遇_BossEncounterConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F25" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G25" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H25" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I25" s="118" t="str">
+      <x:c r="F25" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G25" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H25" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I25" s="120" t="str">
         <x:v>TbBossEncounter generated from Excel</x:v>
       </x:c>
-      <x:c r="J25" s="118"/>
-      <x:c r="K25" s="118"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="118"/>
-      <x:c r="B26" s="118" t="str">
+      <x:c r="J25" s="120"/>
+      <x:c r="K25" s="120"/>
+    </x:row>
+    <x:row r="26" ht="24" customHeight="1">
+      <x:c r="A26" s="120"/>
+      <x:c r="B26" s="120" t="str">
         <x:v>TbExperienceLevel</x:v>
       </x:c>
-      <x:c r="C26" s="118" t="str">
+      <x:c r="C26" s="120" t="str">
         <x:v>ExperienceLevelConfig</x:v>
       </x:c>
-      <x:c r="D26" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E26" s="118" t="str">
+      <x:c r="D26" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E26" s="120" t="str">
         <x:v>Tables/j_经验等级_ExperienceLevelConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F26" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G26" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H26" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I26" s="118" t="str">
+      <x:c r="F26" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G26" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H26" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I26" s="120" t="str">
         <x:v>TbExperienceLevel generated from Excel</x:v>
       </x:c>
-      <x:c r="J26" s="118"/>
-      <x:c r="K26" s="118"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="118"/>
-      <x:c r="B27" s="118" t="str">
+      <x:c r="J26" s="120"/>
+      <x:c r="K26" s="120"/>
+    </x:row>
+    <x:row r="27" ht="24" customHeight="1">
+      <x:c r="A27" s="120"/>
+      <x:c r="B27" s="120" t="str">
         <x:v>TbDropProfile</x:v>
       </x:c>
-      <x:c r="C27" s="118" t="str">
+      <x:c r="C27" s="120" t="str">
         <x:v>DropProfileConfig</x:v>
       </x:c>
-      <x:c r="D27" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E27" s="118" t="str">
+      <x:c r="D27" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E27" s="120" t="str">
         <x:v>Tables/d_掉落_DropProfileConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F27" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G27" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H27" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I27" s="118" t="str">
+      <x:c r="F27" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G27" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H27" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I27" s="120" t="str">
         <x:v>TbDropProfile generated from Excel</x:v>
       </x:c>
-      <x:c r="J27" s="118"/>
-      <x:c r="K27" s="118"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="118"/>
-      <x:c r="B28" s="118" t="str">
+      <x:c r="J27" s="120"/>
+      <x:c r="K27" s="120"/>
+    </x:row>
+    <x:row r="28" ht="24" customHeight="1">
+      <x:c r="A28" s="120"/>
+      <x:c r="B28" s="120" t="str">
         <x:v>TbUpgradePool</x:v>
       </x:c>
-      <x:c r="C28" s="118" t="str">
+      <x:c r="C28" s="120" t="str">
         <x:v>UpgradePoolConfig</x:v>
       </x:c>
-      <x:c r="D28" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E28" s="118" t="str">
+      <x:c r="D28" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E28" s="120" t="str">
         <x:v>Tables/s_升级池_UpgradePoolConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F28" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G28" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H28" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I28" s="118" t="str">
+      <x:c r="F28" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G28" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H28" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I28" s="120" t="str">
         <x:v>TbUpgradePool generated from Excel</x:v>
       </x:c>
-      <x:c r="J28" s="118"/>
-      <x:c r="K28" s="118"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="118"/>
-      <x:c r="B29" s="118" t="str">
+      <x:c r="J28" s="120"/>
+      <x:c r="K28" s="120"/>
+    </x:row>
+    <x:row r="29" ht="24" customHeight="1">
+      <x:c r="A29" s="120"/>
+      <x:c r="B29" s="120" t="str">
         <x:v>TbUpgradeOption</x:v>
       </x:c>
-      <x:c r="C29" s="118" t="str">
+      <x:c r="C29" s="120" t="str">
         <x:v>UpgradeOptionConfig</x:v>
       </x:c>
-      <x:c r="D29" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E29" s="118" t="str">
+      <x:c r="D29" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E29" s="120" t="str">
         <x:v>Tables/s_升级选项_UpgradeOptionConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F29" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G29" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H29" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I29" s="118" t="str">
+      <x:c r="F29" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G29" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H29" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I29" s="120" t="str">
         <x:v>TbUpgradeOption generated from Excel</x:v>
       </x:c>
-      <x:c r="J29" s="118"/>
-      <x:c r="K29" s="118"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="118"/>
-      <x:c r="B30" s="118" t="str">
+      <x:c r="J29" s="120"/>
+      <x:c r="K29" s="120"/>
+    </x:row>
+    <x:row r="30" ht="24" customHeight="1">
+      <x:c r="A30" s="120"/>
+      <x:c r="B30" s="120" t="str">
         <x:v>TbCombatUiSet</x:v>
       </x:c>
-      <x:c r="C30" s="118" t="str">
+      <x:c r="C30" s="120" t="str">
         <x:v>CombatUiSetConfig</x:v>
       </x:c>
-      <x:c r="D30" s="119" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E30" s="118" t="str">
+      <x:c r="D30" s="121" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E30" s="120" t="str">
         <x:v>Tables/z_战斗界面_CombatUiSetConfig.xlsx</x:v>
       </x:c>
-      <x:c r="F30" s="118" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G30" s="118" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H30" s="118" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I30" s="118" t="str">
+      <x:c r="F30" s="120" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G30" s="120" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H30" s="120" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I30" s="120" t="str">
         <x:v>TbCombatUiSet generated from Excel</x:v>
       </x:c>
-      <x:c r="J30" s="118"/>
-      <x:c r="K30" s="118"/>
+      <x:c r="J30" s="120"/>
+      <x:c r="K30" s="120"/>
+    </x:row>
+    <x:row r="31" ht="24" customHeight="1">
+      <x:c r="A31"/>
+      <x:c r="B31"/>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
+      <x:c r="E31"/>
+      <x:c r="F31"/>
+      <x:c r="G31"/>
+      <x:c r="H31"/>
+      <x:c r="I31"/>
+      <x:c r="J31"/>
+      <x:c r="K31"/>
+    </x:row>
+    <x:row r="32" ht="24" customHeight="1">
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+    </x:row>
+    <x:row r="33" ht="24" customHeight="1">
+      <x:c r="A33"/>
+      <x:c r="B33"/>
+      <x:c r="C33"/>
+      <x:c r="D33"/>
+      <x:c r="E33"/>
+      <x:c r="F33"/>
+      <x:c r="G33"/>
+      <x:c r="H33"/>
+      <x:c r="I33"/>
+      <x:c r="J33"/>
+      <x:c r="K33"/>
+    </x:row>
+    <x:row r="34" ht="24" customHeight="1">
+      <x:c r="A34"/>
+      <x:c r="B34"/>
+      <x:c r="C34"/>
+      <x:c r="D34"/>
+      <x:c r="E34"/>
+      <x:c r="F34"/>
+      <x:c r="G34"/>
+      <x:c r="H34"/>
+      <x:c r="I34"/>
+      <x:c r="J34"/>
+      <x:c r="K34"/>
+    </x:row>
+    <x:row r="35" ht="24" customHeight="1">
+      <x:c r="A35"/>
+      <x:c r="B35"/>
+      <x:c r="C35"/>
+      <x:c r="D35"/>
+      <x:c r="E35"/>
+      <x:c r="F35"/>
+      <x:c r="G35"/>
+      <x:c r="H35"/>
+      <x:c r="I35"/>
+      <x:c r="J35"/>
+      <x:c r="K35"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36"/>
+      <x:c r="B36" t="str">
+        <x:v>TbRunWeapon</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>RunWeaponConfig</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>Tables/j_局内武器_RunWeaponConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G36" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H36" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I36" t="str">
+        <x:v>局内构筑正式配置</x:v>
+      </x:c>
+      <x:c r="J36"/>
+      <x:c r="K36"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37"/>
+      <x:c r="B37" t="str">
+        <x:v>TbRunPassive</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>RunPassiveConfig</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>Tables/j_局内被动_RunPassiveConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F37" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G37" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H37" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I37" t="str">
+        <x:v>局内构筑正式配置</x:v>
+      </x:c>
+      <x:c r="J37"/>
+      <x:c r="K37"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38"/>
+      <x:c r="B38" t="str">
+        <x:v>TbRunBuild</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>RunBuildConfig</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>Tables/j_局内构筑_RunBuildConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F38" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G38" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H38" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>局内构筑正式配置</x:v>
+      </x:c>
+      <x:c r="J38"/>
+      <x:c r="K38"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39"/>
+      <x:c r="B39" t="str">
+        <x:v>TbWeaponEvolution</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>WeaponEvolutionConfig</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>Tables/j_武器进化_WeaponEvolutionConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F39" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G39" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H39" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>局内宝箱武器进化</x:v>
+      </x:c>
+      <x:c r="J39"/>
+      <x:c r="K39"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40"/>
+      <x:c r="B40" t="str">
+        <x:v>TbRunEvent</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>RunEventConfig</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>Tables/j_局内事件_RunEventConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F40" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G40" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H40" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>局内事件与宝箱</x:v>
+      </x:c>
+      <x:c r="J40"/>
+      <x:c r="K40"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41"/>
+      <x:c r="B41" t="str">
+        <x:v>TbChestProfile</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>ChestProfileConfig</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>Tables/j_宝箱规则_ChestProfileConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F41" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G41" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H41" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
+        <x:v>局内事件与宝箱</x:v>
+      </x:c>
+      <x:c r="J41"/>
+      <x:c r="K41"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="B42" t="str">
+        <x:v>TbTribulationSlice</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>TribulationSliceConfig</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>Tables/j_借劫切片_TribulationSliceConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F42" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G42" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H42" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I42" t="str">
+        <x:v>借劫炼器体验切片</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="B43" t="str">
+        <x:v>TbTribulationRule</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>TribulationRuleConfig</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>Tables/j_借劫规则_TribulationRuleConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G43" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H43" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I43" t="str">
+        <x:v>借劫炼器体验切片</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="B44" t="str">
+        <x:v>TbTribulationSignature</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>TribulationSignatureConfig</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>Tables/j_借劫职业_TribulationSignatureConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G44" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
+        <x:v>借劫炼器体验切片</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="B45" t="str">
+        <x:v>TbTribulationRefinement</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>TribulationRefinementConfig</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>Tables/j_借劫炼器_TribulationRefinementConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G45" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H45" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I45" t="str">
+        <x:v>借劫炼器体验切片</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="B46" t="str">
+        <x:v>TbTribulationUi</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>TribulationUiConfig</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>Tables/z_借劫界面_TribulationUiConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F46" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>借劫炼器体验切片</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="B47" t="inlineStr">
+        <x:is>
+          <x:t>TbCombatRender</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C47" t="inlineStr">
+        <x:is>
+          <x:t>CombatRenderConfig</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D47" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E47" t="inlineStr">
+        <x:is>
+          <x:t>Tables/z_表现层级_CombatRenderConfig.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F47" t="inlineStr">
+        <x:is>
+          <x:t>id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G47" t="inlineStr">
+        <x:is>
+          <x:t>map</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H47" t="inlineStr">
+        <x:is>
+          <x:t>c</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I47" t="inlineStr">
+        <x:is>
+          <x:t>模型与技能片段独立渲染层级</x:t>
+        </x:is>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="1" r:id="Rfa0aa16de4ad4813"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="1" r:id="R4d8f76e013954860"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2368,12 +2368,12 @@
     <x:row r="47">
       <x:c r="B47" t="inlineStr">
         <x:is>
-          <x:t>TbCombatRender</x:t>
+          <x:t xml:space="preserve">TbCombatRender</x:t>
         </x:is>
       </x:c>
       <x:c r="C47" t="inlineStr">
         <x:is>
-          <x:t>CombatRenderConfig</x:t>
+          <x:t xml:space="preserve">CombatRenderConfig</x:t>
         </x:is>
       </x:c>
       <x:c r="D47" t="b">
@@ -2381,29 +2381,174 @@
       </x:c>
       <x:c r="E47" t="inlineStr">
         <x:is>
-          <x:t>Tables/z_表现层级_CombatRenderConfig.xlsx</x:t>
+          <x:t xml:space="preserve">Tables/z_表现层级_CombatRenderConfig.xlsx</x:t>
         </x:is>
       </x:c>
       <x:c r="F47" t="inlineStr">
         <x:is>
-          <x:t>id</x:t>
+          <x:t xml:space="preserve">id</x:t>
         </x:is>
       </x:c>
       <x:c r="G47" t="inlineStr">
         <x:is>
-          <x:t>map</x:t>
+          <x:t xml:space="preserve">map</x:t>
         </x:is>
       </x:c>
       <x:c r="H47" t="inlineStr">
         <x:is>
-          <x:t>c</x:t>
+          <x:t xml:space="preserve">c</x:t>
         </x:is>
       </x:c>
       <x:c r="I47" t="inlineStr">
         <x:is>
-          <x:t>模型与技能片段独立渲染层级</x:t>
+          <x:t xml:space="preserve">模型与技能片段独立渲染层级</x:t>
         </x:is>
       </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48"/>
+      <x:c r="B48" t="str">
+        <x:v>TbDraftPolicy</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>DraftPolicyConfig</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E48" t="str">
+        <x:v>Tables/s_抽选策略_DraftPolicyConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F48" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G48" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H48" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I48" t="str">
+        <x:v>构筑反馈P0</x:v>
+      </x:c>
+      <x:c r="J48"/>
+      <x:c r="K48"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49"/>
+      <x:c r="B49" t="str">
+        <x:v>TbUpgradeRule</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>UpgradeRuleConfig</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E49" t="str">
+        <x:v>Tables/s_选卡资格_UpgradeRuleConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F49" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G49" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H49" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I49" t="str">
+        <x:v>构筑反馈P0</x:v>
+      </x:c>
+      <x:c r="J49"/>
+      <x:c r="K49"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50"/>
+      <x:c r="B50" t="str">
+        <x:v>TbMechanismCard</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>MechanismCardConfig</x:v>
+      </x:c>
+      <x:c r="D50" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E50" t="str">
+        <x:v>Tables/j_职业修饰_MechanismCardConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F50" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G50" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H50" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I50" t="str">
+        <x:v>构筑反馈P0</x:v>
+      </x:c>
+      <x:c r="J50"/>
+      <x:c r="K50"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51"/>
+      <x:c r="B51" t="str">
+        <x:v>TbContentGoal</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>ContentGoalConfig</x:v>
+      </x:c>
+      <x:c r="D51" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E51" t="str">
+        <x:v>Tables/j_内容目标_ContentGoalConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F51" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G51" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H51" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I51" t="str">
+        <x:v>构筑反馈P0</x:v>
+      </x:c>
+      <x:c r="J51"/>
+      <x:c r="K51"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52"/>
+      <x:c r="B52" t="str">
+        <x:v>TbBuildFeedbackUi</x:v>
+      </x:c>
+      <x:c r="C52" t="str">
+        <x:v>BuildFeedbackUiConfig</x:v>
+      </x:c>
+      <x:c r="D52" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E52" t="str">
+        <x:v>Tables/z_构筑反馈_BuildFeedbackUiConfig.xlsx</x:v>
+      </x:c>
+      <x:c r="F52" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G52" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H52" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I52" t="str">
+        <x:v>构筑反馈P0</x:v>
+      </x:c>
+      <x:c r="J52"/>
+      <x:c r="K52"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
